--- a/data/trans_bre/P05B_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P05B_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>-0,49</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-24,28%</t>
+          <t>-24,26%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 4,28</t>
+          <t>-1,59; 4,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,27; -0,21</t>
+          <t>-4,38; -0,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,21</t>
+          <t>-2,07; 1,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 1,19</t>
+          <t>-2,45; 1,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-33,89; 186,84</t>
+          <t>-37,28; 189,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 14,65</t>
+          <t>-100,0; 14,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 313,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-75,01; 116,04</t>
+          <t>-74,32; 107,91</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>254,91%</t>
+          <t>228,13%</t>
         </is>
       </c>
     </row>
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 3,23</t>
+          <t>-2,36; 3,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 2,26</t>
+          <t>-2,21; 2,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 3,52</t>
+          <t>-0,0; 3,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,21</t>
+          <t>0,09; 2,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,5; 183,8</t>
+          <t>-54,0; 166,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-73,99; 284,94</t>
+          <t>-71,08; 241,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,93; 2051,06</t>
+          <t>-52,9; —</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>-6,21%</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 8,57</t>
+          <t>0,95; 8,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 2,58</t>
+          <t>-0,84; 2,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; -0,15</t>
+          <t>-2,15; -0,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,59</t>
+          <t>-1,31; 1,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,37; 611,27</t>
+          <t>15,3; 567,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 948,65</t>
+          <t>-100,0; 889,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 367,76</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>38,95%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 3,26</t>
+          <t>-0,42; 3,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,28</t>
+          <t>-0,63; 2,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 1,97</t>
+          <t>-0,83; 2,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 0,78</t>
+          <t>-0,55; 1,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 123,99</t>
+          <t>-11,23; 127,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,85; 180,4</t>
+          <t>-27,85; 202,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,55; 124,09</t>
+          <t>-32,32; 130,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,62; 138,5</t>
+          <t>-45,73; 216,46</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>55,22%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,37</t>
+          <t>0,31; 5,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 1,16</t>
+          <t>-1,29; 1,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,67</t>
+          <t>-1,12; 1,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,22</t>
+          <t>-0,68; 1,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,6; 505,2</t>
+          <t>1,12; 471,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-82,74; 302,19</t>
+          <t>-76,4; 246,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-46,69; 204,09</t>
+          <t>-52,56; 174,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-60,14; 243,4</t>
+          <t>-45,28; 411,17</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,64</t>
+          <t>-1,23; 3,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,33</t>
+          <t>-2,36; 1,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,61</t>
+          <t>1,11; 3,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,25</t>
+          <t>0,29; 1,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,25; 238,65</t>
+          <t>-25,99; 213,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,19; 230,68</t>
+          <t>-70,53; 168,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,64</t>
+          <t>0,82; 2,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,61</t>
+          <t>-0,62; 0,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,42</t>
+          <t>0,15; 1,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,65</t>
+          <t>-0,23; 0,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,45; 105,58</t>
+          <t>22,24; 100,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-34,95; 44,64</t>
+          <t>-32,39; 55,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 129,6</t>
+          <t>8,32; 128,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-27,93; 85,61</t>
+          <t>-19,5; 99,02</t>
         </is>
       </c>
     </row>
